--- a/earth-pipeline/HowUnitTestPipelineWorks.xlsx
+++ b/earth-pipeline/HowUnitTestPipelineWorks.xlsx
@@ -5,24 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cuifawei-d\setup\code\earth-unittest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cuifawei-d\documents\earth-pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033FAA44-DD4E-4208-A7B9-46487AF8F20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B7578-0692-457D-BAA1-D775985C466F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vs-project" sheetId="1" r:id="rId1"/>
     <sheet name="project-settings" sheetId="7" r:id="rId2"/>
     <sheet name="nuget" sheetId="2" r:id="rId3"/>
-    <sheet name="Nunit" sheetId="3" r:id="rId4"/>
-    <sheet name="code coverage" sheetId="4" r:id="rId5"/>
-    <sheet name="test-gen" sheetId="5" r:id="rId6"/>
-    <sheet name="cloud-temp" sheetId="6" r:id="rId7"/>
-    <sheet name="pipeline" sheetId="9" r:id="rId8"/>
-    <sheet name="pipeline-PR_Pipeline.yml" sheetId="10" r:id="rId9"/>
-    <sheet name="PR_Gate.yml" sheetId="11" r:id="rId10"/>
+    <sheet name="code coverage" sheetId="4" r:id="rId4"/>
+    <sheet name="test-gen" sheetId="5" r:id="rId5"/>
+    <sheet name="cloud-temp" sheetId="6" r:id="rId6"/>
+    <sheet name="pipeline" sheetId="9" r:id="rId7"/>
+    <sheet name="pipeline-PR_Pipeline.yml" sheetId="10" r:id="rId8"/>
+    <sheet name="PR_Gate.yml" sheetId="11" r:id="rId9"/>
+    <sheet name="pipeline-Nunit" sheetId="3" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="222">
   <si>
     <r>
       <t xml:space="preserve">VS 在加载项目时，尝试导入一个共享的 MSBuild 目标文件 </t>
@@ -1359,12 +1359,1274 @@
   <si>
     <t>2. parameters 传递的参数</t>
   </si>
+  <si>
+    <t>Mapping each pipeline step from yml</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>parameters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentcapability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: []</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentDemand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: []</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Version</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>''</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ComponentName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>''</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TargetTestFolder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>''</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>csproj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: []</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RunModuleTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'false'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>jobs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>GatedException.yml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parameters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentcapability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.agentcapability }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentDemand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.agentDemand }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Version</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.Version }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ComponentName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.ComponentName }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Solution</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.ComponentName }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionPath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'ExtInf/${{ parameters.ComponentName }}Inf.sln'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionPath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Src/${{ parameters.ComponentName }}Impl.sln'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ if eq(parameters.RunModuleTest, 'true') }}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Module_Nunit_PR.yml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parameters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:      </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentcapability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.agentcapability }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>agentDemand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.agentDemand }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Version</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.Version }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ComponentName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.ComponentName }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TargetTestFolder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.TargetTestFolder }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>csproj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.csproj }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Solution</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">          - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.ComponentName }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionPath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'ExtInf/${{ parameters.ComponentName }}Inf.sln'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionPath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Src/${{ parameters.ComponentName }}Impl.sln'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ if eq(parameters.RunModuleTest, 'false') }}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Nunit_PR1.yml     </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TICS1.yml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dependsOn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Build</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>timeoutInMinutes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Checkout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>self</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>csproj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${{ parameters.csproj }}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>solutionPath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Src/${{ parameters.ComponentName }}Impl.sln'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ResharperPR1.yml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProjectSettings_PR1.yml</t>
+    </r>
+  </si>
+  <si>
+    <t>变量组，有很多变量在这里</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1451,8 +2713,38 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF7EE787"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFA5D6FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFC9D1D9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1471,6 +2763,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF121314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1484,7 +2782,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1507,6 +2805,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1802,55 +3112,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>456381</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>10910</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E6B0C0-3481-07FA-8616-17ED29A6E296}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1160145"/>
-          <a:ext cx="6552381" cy="4165715"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -1940,7 +3201,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2033,7 +3294,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2346,7 +3607,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2359,7 +3620,7 @@
       <xdr:col>35</xdr:col>
       <xdr:colOff>37218</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>135255</xdr:rowOff>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2401,9 +3662,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>555200</xdr:colOff>
+      <xdr:colOff>551390</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>92670</xdr:rowOff>
+      <xdr:rowOff>96480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2447,7 +3708,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>36883</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>135255</xdr:rowOff>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2489,7 +3750,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>210080</xdr:colOff>
+      <xdr:colOff>206270</xdr:colOff>
       <xdr:row>160</xdr:row>
       <xdr:rowOff>722</xdr:rowOff>
     </xdr:to>
@@ -2533,7 +3794,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:colOff>434340</xdr:colOff>
       <xdr:row>161</xdr:row>
       <xdr:rowOff>74812</xdr:rowOff>
     </xdr:to>
@@ -2568,10 +3829,54 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>560305</xdr:colOff>
+      <xdr:row>229</xdr:row>
+      <xdr:rowOff>17698</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566CECC6-5996-375D-D104-A2C4048B1DE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="28460700"/>
+          <a:ext cx="13361905" cy="10819048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2829,6 +4134,236 @@
         <a:xfrm>
           <a:off x="9601200" y="38033325"/>
           <a:ext cx="5394286" cy="5230476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>66689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>132467</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F8D1A67-C074-1C15-D7AF-077F119BA498}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1266839"/>
+          <a:ext cx="11544300" cy="5209278"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>494476</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>18362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33CDF43A-6CF2-2206-9FE5-0948195B2335}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12801600" y="1200150"/>
+          <a:ext cx="6590476" cy="5504762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>456381</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10910</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E6B0C0-3481-07FA-8616-17ED29A6E296}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1160145"/>
+          <a:ext cx="6552381" cy="4165715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>465371</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>27671</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8527176-087F-1B13-ABE4-BF31EE88E469}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6515100"/>
+          <a:ext cx="10828571" cy="7228571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>503390</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>37238</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51641D6-067C-B26D-901E-E4448E04C178}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14230350"/>
+          <a:ext cx="11476190" cy="6895238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3833,12 +5368,13 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB0BB3B-F96E-4A33-A146-4D11ABB356EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32137F47-3F32-4937-AF61-315CDE07C17B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3891,10 +5427,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32137F47-3F32-4937-AF61-315CDE07C17B}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EFF05D-C5FC-49DA-9E24-2E71164C9C4F}">
+  <dimension ref="B4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3902,13 +5444,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EFF05D-C5FC-49DA-9E24-2E71164C9C4F}">
-  <dimension ref="B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B83E43-670E-4A22-923F-33601DB1C2BA}">
+  <dimension ref="C2:C3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>119</v>
+    <row r="2" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3919,28 +5466,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B83E43-670E-4A22-923F-33601DB1C2BA}">
-  <dimension ref="C2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8DE8B5-61B4-4F58-9B40-36D9D3CAB859}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -3951,9 +5476,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A447339B-1D6E-40C3-97B7-B79BE25ED722}">
-  <dimension ref="A3:U121"/>
+  <dimension ref="A3:U163"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4109,6 +5634,369 @@
     <row r="121" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115ED729-1D35-4D32-A373-FB6A52537485}">
+  <dimension ref="A44:M214"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C44" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C45" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C46" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C47" s="8"/>
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C48" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="8"/>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C56" s="8"/>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="8"/>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="8"/>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C63" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C65" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C66" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C67" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C68" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C69" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C70" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C71" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="7"/>
+    </row>
+    <row r="196" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B214" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4119,354 +6007,459 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115ED729-1D35-4D32-A373-FB6A52537485}">
-  <dimension ref="A44:M214"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB0BB3B-F96E-4A33-A146-4D11ABB356EE}">
+  <dimension ref="A4:B131"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C44" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C45" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="M45" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C46" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C47" s="8"/>
-    </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C48" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C51" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C54" s="8"/>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="8"/>
-    </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="8"/>
-    </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="8"/>
-    </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B101" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B102" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B103" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B104" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B105" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B134" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B143" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B144" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B190" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B193" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B194" s="7"/>
-    </row>
-    <row r="196" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B199" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B200" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B201" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B202" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B203" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B204" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B205" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B206" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B207" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B209" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B210" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B211" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B212" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B213" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B214" t="s">
-        <v>173</v>
+    <row r="4" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="12"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="12"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="12"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="12"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="12"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="12"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="13" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/earth-pipeline/HowUnitTestPipelineWorks.xlsx
+++ b/earth-pipeline/HowUnitTestPipelineWorks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cuifawei-d\documents\earth-pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B7578-0692-457D-BAA1-D775985C466F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0070C0-D259-4D5D-9ECB-AEFE439A4C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,8 @@
     <sheet name="pipeline" sheetId="9" r:id="rId7"/>
     <sheet name="pipeline-PR_Pipeline.yml" sheetId="10" r:id="rId8"/>
     <sheet name="PR_Gate.yml" sheetId="11" r:id="rId9"/>
-    <sheet name="pipeline-Nunit" sheetId="3" r:id="rId10"/>
+    <sheet name="Resharper" sheetId="12" r:id="rId10"/>
+    <sheet name="pipeline-Nunit" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="223">
   <si>
     <r>
       <t xml:space="preserve">VS 在加载项目时，尝试导入一个共享的 MSBuild 目标文件 </t>
@@ -2620,6 +2621,9 @@
   <si>
     <t>变量组，有很多变量在这里</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PR_Gate.yml</t>
   </si>
 </sst>
 </file>
@@ -2960,6 +2964,143 @@
         <a:xfrm>
           <a:off x="0" y="15087600"/>
           <a:ext cx="8914286" cy="4533333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>456381</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10910</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E6B0C0-3481-07FA-8616-17ED29A6E296}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1160145"/>
+          <a:ext cx="6552381" cy="4165715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>465371</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>27671</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8527176-087F-1B13-ABE4-BF31EE88E469}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6515100"/>
+          <a:ext cx="10828571" cy="7228571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>503390</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>37238</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51641D6-067C-B26D-901E-E4448E04C178}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14230350"/>
+          <a:ext cx="11476190" cy="6895238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4242,23 +4383,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>456381</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>10910</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>103848</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>161626</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E6B0C0-3481-07FA-8616-17ED29A6E296}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62163240-C3FE-0431-E9E3-51BF88DD69C8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4274,96 +4415,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1160145"/>
-          <a:ext cx="6552381" cy="4165715"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>465371</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>27671</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8527176-087F-1B13-ABE4-BF31EE88E469}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6515100"/>
-          <a:ext cx="10828571" cy="7228571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>503390</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>37238</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51641D6-067C-B26D-901E-E4448E04C178}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="14230350"/>
-          <a:ext cx="11476190" cy="6895238"/>
+          <a:off x="609600" y="3429000"/>
+          <a:ext cx="7419048" cy="2390476"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5368,6 +5421,98 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A26ABD03-4BD3-4CD9-842A-3E9B9DC60DD0}">
+  <dimension ref="A2:B17"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32137F47-3F32-4937-AF61-315CDE07C17B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
